--- a/product_selector_out/STM32F7x5.xlsx
+++ b/product_selector_out/STM32F7x5.xlsx
@@ -12512,7 +12512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13348,7 +13348,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13700,7 +13700,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F7x5.xlsx
+++ b/product_selector_out/STM32F7x5.xlsx
@@ -7480,9 +7480,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -7817,9 +7817,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -8828,9 +8828,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -9502,9 +9502,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -11187,9 +11187,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -11861,9 +11861,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">

--- a/product_selector_out/STM32F7x5.xlsx
+++ b/product_selector_out/STM32F7x5.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO27"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.61328125" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -5725,6 +5797,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
@@ -6062,6 +6139,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f745ie.pdf</t>
         </is>
       </c>
@@ -6399,12 +6481,17 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f765bg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6427,12 +6514,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6447,9 +6536,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -6501,7 +6589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO27"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6571,6 +6659,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6914,6 +7003,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7011,6 +7105,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7343,7 +7438,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7680,7 +7780,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8017,7 +8122,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8354,7 +8464,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8691,7 +8806,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9028,7 +9148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9365,7 +9490,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9702,7 +9832,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10039,7 +10174,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10376,7 +10516,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10713,7 +10858,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11050,7 +11200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11387,7 +11542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11724,7 +11884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12061,7 +12226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12398,7 +12568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12406,8 +12581,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
